--- a/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +50,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,350 +420,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Пункт проверки</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Да / Нет</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Фактическое значение</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Примечание</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ЧЕК-ЛИСТ ПРОВЕРКИ ОРГТЕХНИКИ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Инвентарный номер</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>67+</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Организация: Этажи</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Kyocera ECOSYS M3040dn</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Серийный номер</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LS67Y43279</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Дата проверки: 22.06.2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Местоположение</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Риелторы (Тюмень)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Дата проверки</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>22.06.2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Инвентарный номер: 67+</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Модель соответствует учетным данным</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Kyocera ECOSYS M3040dn</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Модель: Kyocera ECOSYS M3040dn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Серийный номер соответствует</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LS67Y43279</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Серийный номер: LS67Y43279</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Инвентарный номер соответствует</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>67+</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Местоположение: Риелторы (Тюмень)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Место размещения соответствует</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Риелторы (Тюмень)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Офис: Тюмень</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Офис соответствует</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Подразделение: Риелторы</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Подразделение соответствует</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Риелторы</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="A12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Показания счетчика за предыдущий месяц зафиксированы</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>272339</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Проверка:</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Показания счетчика за отчетный месяц зафиксированы</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>272864</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Модель соответствует учетным данным. Факт: Kyocera ECOSYS M3040dn</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Количество отпечатков за период проверено</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Серийный номер соответствует. Факт: LS67Y43279</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Устройство включено и исправно</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Инвентарный номер соответствует. Факт: 67+</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Печать / сканирование выполняется</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Место размещения соответствует. Факт: Риелторы (Тюмень)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ответственный сотрудник определен</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Офис соответствует. Факт: Тюмень</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Внешний вид и комплектность в норме</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Подразделение соответствует. Факт: Риелторы</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Замечания отсутствуют</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Счетчик (предыдущий месяц) зафиксирован. Факт: 272339</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Проверил</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Счетчик (отчетный месяц) зафиксирован. Факт: 272864</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Подпись ответственного</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Кол-во отпечатков проверено. Факт: 525</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Устройство включено и исправно</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Печать / сканирование выполняется</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ ] Ответственный сотрудник определен. Факт: </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Внешний вид и комплектность в норме</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Замечания отсутствуют</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Проверил: __________________ / __________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Подпись ответственного: __________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -429,199 +429,511 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЧЕК-ЛИСТ ПРОВЕРКИ ОРГТЕХНИКИ</t>
+          <t>┌─────────────────────────────────────────────────────────────┐</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Организация: Этажи</t>
+          <t>│ ЧЕК-ЛИСТ БАЗОВОЙ ПРОВЕРКИ АППАРАТА (5-7 минут)              │</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>└─────────────────────────────────────────────────────────────┘</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Дата проверки: 22.06.2026</t>
-        </is>
-      </c>
+      <c r="A4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>═══════════════════════════════════════════════════════════════</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Инвентарный номер: 67+</t>
+          <t>БЛОК А. РЕКВИЗИТЫ АППАРАТА (для дальнейшего анализа)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Модель: Kyocera ECOSYS M3040dn</t>
+          <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Серийный номер: LS67Y43279</t>
+          <t xml:space="preserve">Модель:                  Kyocera ECOSYS M3040dn               </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Местоположение: Риелторы (Тюмень)</t>
+          <t xml:space="preserve">Серийный номер:          LS67Y43279                           </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Офис: Тюмень</t>
+          <t xml:space="preserve">Инвентарный номер:       67+                                  </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Подразделение: Риелторы</t>
+          <t xml:space="preserve">Локация (офис/кабинет):  Риелторы (Тюмень)                    </t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Модель картриджа:        _____________________________________</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Проверка:</t>
+          <t>Текущий ресурс картриджа (%): ________________________________</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>[ ] Модель соответствует учетным данным. Факт: Kyocera ECOSYS M3040dn</t>
+          <t>Дата последнего ТО:      _____________________________________</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>[ ] Серийный номер соответствует. Факт: LS67Y43279</t>
+          <t>Дата последней замены ЗИП: ___________________________________</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>[ ] Инвентарный номер соответствует. Факт: 67+</t>
+          <t>Ответственный у Заказчика: ___________________________________</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>[ ] Место размещения соответствует. Факт: Риелторы (Тюмень)</t>
+          <t>Контакт (тел/email):     _____________________________________</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>[ ] Офис соответствует. Факт: Тюмень</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>[ ] Подразделение соответствует. Факт: Риелторы</t>
+          <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>[ ] Счетчик (предыдущий месяц) зафиксирован. Факт: 272339</t>
+          <t>БЛОК Б. ПРОВЕРКА ПО ШАГАМ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>[ ] Счетчик (отчетный месяц) зафиксирован. Факт: 272864</t>
+          <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>[ ] Кол-во отпечатков проверено. Факт: 525</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>[ ] Устройство включено и исправно</t>
+          <t>ШАГ 1. ВНЕШНИЙ ОСМОТР (30 сек)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>[ ] Печать / сканирование выполняется</t>
+          <t xml:space="preserve">  □ Корпус, крышки, лотки — визуально целые</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">[ ] Ответственный сотрудник определен. Факт: </t>
+          <t xml:space="preserve">  □ Кабели подключены надежно, без перегибов</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>[ ] Внешний вид и комплектность в норме</t>
+          <t xml:space="preserve">  □ Вокруг аппарата чисто, нет мусора, скрепок, скоб</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>[ ] Замечания отсутствуют</t>
-        </is>
-      </c>
+      <c r="A27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ШАГ 2. СЧЕТЧИКИ (1 мин)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Проверил: __________________ / __________________</t>
+          <t xml:space="preserve">  □ Открыть меню → Отчет → Страница состояния (Kyocera)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Подпись ответственного: __________________</t>
+          <t xml:space="preserve">     или Меню → Reports → Usage Report (HP)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Записать: Total / ЧБ / Цвет / Сканер</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Сверить с данными в файле "Этажи покопийка AI.xlsx"</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (расхождение &gt; 5% — пометить в карточке)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ШАГ 3. ТЕСТОВАЯ ПЕЧАТЬ (1 мин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Распечатать тестовую страницу из встроенного меню</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Оценить: плотность, полосы, фон, регистрация</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Проверить закрепление тонера (провести пальцем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Для цветных — напечатать страницу качества цвета</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ШАГ 4. ТЕСТ СКАНИРОВАНИЯ (1 мин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Положить лист A4 на стекло / в ADF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Отсканировать на email / в сетевую папку</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Проверить: нет полос, захват ADF без перекоса</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ШАГ 5. ФИЗИКА (1-2 мин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Открыть переднюю крышку, заглянуть внутрь</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Осмотреть ролики захвата (лысые? грязные?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Осмотреть термоузел (следы тонера, нагар?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Проверить дуплекс (нет ли замятой бумаги)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Понюхать (запах гари = проблема с печкой)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ШАГ 6. СУБЪЕКТИВНАЯ ОЦЕНКА (30 сек)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Оценить физическое состояние (1-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Оценить качество печати (1-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Оценить качество сканирования (1-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Выставить общую оценку (1-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ШАГ 7. ФИКСАЦИЯ В КАРТОЧКЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Заполнить все поля карточки аппарата</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Отметить все применимые пункты "План действий"</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Указать приоритет и срок выполнения</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  □ Сфотографировать дефекты (если есть)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>═══════════════════════════════════════════════════════════════</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>🚨 КРАСНЫЕ ФЛАГИ (немедленная эскалация Наталье, руководителю):</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Аппарат не включается / нет реакции</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Счетчик не изменился с прошлого месяца (0 отпечатков)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Сильный запах гари, дым</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Треск, скрежет, посторонние звуки</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Явное физическое повреждение корпуса/лотков</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Оценка "1" по любому из параметров</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Аппарат отсутствует на месте (пропажа / перемещение без согласования)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Конфликт с Заказчиком / отказ в доступе</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Риск срыва SLA (критичный фронт-офис не работает)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Канал эскалации: мессенджер MAX → чат "Этажи_Сервис"</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Время реакции Натальи: до 30 минут в рабочее время</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>═══════════════════════════════════════════════════════════════</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
@@ -17,17 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,520 +413,1012 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Отметка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>┌─────────────────────────────────────────────────────────────┐</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>│ ЧЕК-ЛИСТ БАЗОВОЙ ПРОВЕРКИ АППАРАТА (5-7 минут)              │</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>└─────────────────────────────────────────────────────────────┘</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>БЛОК А. РЕКВИЗИТЫ АППАРАТА (для дальнейшего анализа)</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Модель:                  Kyocera ECOSYS M3040dn               </t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kyocera ECOSYS M3040dn</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Серийный номер:          LS67Y43279                           </t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Серийный номер</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LS67Y43279</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Инвентарный номер:       67+                                  </t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Инвентарный номер</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>67+</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Локация (офис/кабинет):  Риелторы (Тюмень)                    </t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Локация (офис/кабинет)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Риелторы (Тюмень)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Модель картриджа:        _____________________________________</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Модель картриджа</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Текущий ресурс картриджа (%): ________________________________</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Текущий ресурс картриджа (%)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Дата последнего ТО:      _____________________________________</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Дата последнего ТО</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Дата последней замены ЗИП: ___________________________________</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Дата последней замены ЗИП</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Ответственный у Заказчика: ___________________________________</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ответственный у Заказчика</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Контакт (тел/email):     _____________________________________</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Контакт (тел/email)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>═══════════════════════════════════════════════════════════════</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>БЛОК Б. ПРОВЕРКА ПО ШАГАМ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>БЛОК Б. ПРОВЕРКА ПО ШАГАМ</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ШАГ 1. ВНЕШНИЙ ОСМОТР (30 сек)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Корпус, крышки, лотки — визуально целые</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Кабели подключены надежно, без перегибов</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Вокруг аппарата чисто, нет мусора, скрепок, скоб</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ШАГ 2. СЧЕТЧИКИ (1 мин)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Открыть меню → Отчет → Страница состояния (Kyocera)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>или Меню → Reports → Usage Report (HP)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Записать: Total / ЧБ / Цвет / Сканер</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Сверить с данными в файле "Этажи покопийка AI.xlsx"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>(расхождение &gt; 5% — пометить в карточке)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ШАГ 3. ТЕСТОВАЯ ПЕЧАТЬ (1 мин)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Распечатать тестовую страницу из встроенного меню</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Оценить: плотность, полосы, фон, регистрация</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Проверить закрепление тонера (провести пальцем)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Для цветных — напечатать страницу качества цвета</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ШАГ 4. ТЕСТ СКАНИРОВАНИЯ (1 мин)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Положить лист A4 на стекло / в ADF</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Отсканировать на email / в сетевую папку</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Проверить: нет полос, захват ADF без перекоса</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ШАГ 5. ФИЗИКА (1-2 мин)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Открыть переднюю крышку, заглянуть внутрь</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Осмотреть ролики захвата (лысые? грязные?)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Осмотреть термоузел (следы тонера, нагар?)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Проверить дуплекс (нет ли замятой бумаги)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Понюхать (запах гари = проблема с печкой)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ШАГ 6. СУБЪЕКТИВНАЯ ОЦЕНКА (30 сек)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Оценить физическое состояние (1-5)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Оценить качество печати (1-5)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Оценить качество сканирования (1-5)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Выставить общую оценку (1-5)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ШАГ 7. ФИКСАЦИЯ В КАРТОЧКЕ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Заполнить все поля карточки аппарата</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Отметить все применимые пункты "План действий"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Указать приоритет и срок выполнения</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Сфотографировать дефекты (если есть)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 1. ВНЕШНИЙ ОСМОТР (30 сек)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Корпус, крышки, лотки — визуально целые</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Кабели подключены надежно, без перегибов</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Вокруг аппарата чисто, нет мусора, скрепок, скоб</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 2. СЧЕТЧИКИ (1 мин)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Открыть меню → Отчет → Страница состояния (Kyocera)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     или Меню → Reports → Usage Report (HP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Записать: Total / ЧБ / Цвет / Сканер</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Сверить с данными в файле "Этажи покопийка AI.xlsx"</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     (расхождение &gt; 5% — пометить в карточке)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 3. ТЕСТОВАЯ ПЕЧАТЬ (1 мин)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Распечатать тестовую страницу из встроенного меню</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Оценить: плотность, полосы, фон, регистрация</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Проверить закрепление тонера (провести пальцем)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Для цветных — напечатать страницу качества цвета</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 4. ТЕСТ СКАНИРОВАНИЯ (1 мин)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Положить лист A4 на стекло / в ADF</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Отсканировать на email / в сетевую папку</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Проверить: нет полос, захват ADF без перекоса</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 5. ФИЗИКА (1-2 мин)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Открыть переднюю крышку, заглянуть внутрь</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Осмотреть ролики захвата (лысые? грязные?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Осмотреть термоузел (следы тонера, нагар?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Проверить дуплекс (нет ли замятой бумаги)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Понюхать (запах гари = проблема с печкой)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 6. СУБЪЕКТИВНАЯ ОЦЕНКА (30 сек)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Оценить физическое состояние (1-5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Оценить качество печати (1-5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Оценить качество сканирования (1-5)</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Выставить общую оценку (1-5)</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>🚨 КРАСНЫЕ ФЛАГИ (немедленная эскалация Наталье, руководителю)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>• Аппарат не включается / нет реакции</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>ШАГ 7. ФИКСАЦИЯ В КАРТОЧКЕ</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>• Счетчик не изменился с прошлого месяца (0 отпечатков)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Заполнить все поля карточки аппарата</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>• Сильный запах гари, дым</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Отметить все применимые пункты "План действий"</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>• Треск, скрежет, посторонние звуки</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Указать приоритет и срок выполнения</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>• Явное физическое повреждение корпуса/лотков</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  □ Сфотографировать дефекты (если есть)</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>• Оценка "1" по любому из параметров</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>• Аппарат отсутствует на месте (пропажа / перемещение без согласования)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>• Конфликт с Заказчиком / отказ в доступе</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>• Риск срыва SLA (критичный фронт-офис не работает)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Канал эскалации</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>мессенджер MAX → чат "Этажи_Сервис"</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Время реакции Натальи</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>до 30 минут в рабочее время</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>🚨 КРАСНЫЕ ФЛАГИ (немедленная эскалация Наталье, руководителю):</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Аппарат не включается / нет реакции</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Счетчик не изменился с прошлого месяца (0 отпечатков)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Сильный запах гари, дым</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Треск, скрежет, посторонние звуки</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Явное физическое повреждение корпуса/лотков</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Оценка "1" по любому из параметров</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Аппарат отсутствует на месте (пропажа / перемещение без согласования)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Конфликт с Заказчиком / отказ в доступе</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Риск срыва SLA (критичный фронт-офис не работает)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Канал эскалации: мессенджер MAX → чат "Этажи_Сервис"</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>Время реакции Натальи: до 30 минут в рабочее время</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
@@ -413,13 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,6 +441,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Отметка</t>
         </is>
       </c>
@@ -457,6 +463,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,6 +478,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -485,6 +493,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -499,6 +508,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -513,6 +523,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -527,6 +538,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -545,6 +557,7 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -563,6 +576,7 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,6 +595,7 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -599,6 +614,7 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -613,6 +629,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -627,6 +644,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -641,6 +659,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -655,6 +674,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -669,6 +689,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -683,6 +704,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -697,6 +719,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -711,6 +734,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -725,6 +749,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -739,6 +764,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -753,6 +779,11 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -767,6 +798,11 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -781,6 +817,11 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -795,6 +836,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -809,6 +851,11 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -823,6 +870,7 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -837,6 +885,11 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -851,6 +904,11 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -865,6 +923,7 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -879,6 +938,7 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -893,6 +953,11 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -907,6 +972,11 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -921,6 +991,11 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -935,6 +1010,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -949,6 +1029,7 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -963,6 +1044,11 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -977,6 +1063,11 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -991,6 +1082,11 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1005,6 +1101,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1019,6 +1116,11 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1033,6 +1135,11 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1047,6 +1154,11 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1061,6 +1173,11 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1075,6 +1192,11 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1089,6 +1211,7 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1103,6 +1226,11 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1117,6 +1245,11 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1131,6 +1264,11 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1145,6 +1283,11 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1159,6 +1302,7 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1173,6 +1317,11 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1187,6 +1336,11 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1201,6 +1355,11 @@
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1215,6 +1374,11 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1229,6 +1393,7 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1243,6 +1408,7 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1257,6 +1423,7 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1271,6 +1438,7 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1285,6 +1453,7 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1299,6 +1468,7 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1313,6 +1483,7 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1327,6 +1498,7 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1341,6 +1513,7 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1355,6 +1528,7 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1369,6 +1543,7 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1387,6 +1562,7 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1405,6 +1581,7 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1419,6 +1596,7 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/checklists/TEST_Checklist_67plus_LS67Y43279.xlsx
@@ -413,38 +413,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Поле</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Значение</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Ед.</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>Отметка</t>
         </is>
@@ -453,1150 +447,626 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>┌─────────────────────────────────────────────────────────────┐</t>
-        </is>
-      </c>
+          <t>ЧЕК-ЛИСТ БАЗОВОЙ ПРОВЕРКИ АППАРАТА (5-7 минут)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>│ ЧЕК-ЛИСТ БАЗОВОЙ ПРОВЕРКИ АППАРАТА (5-7 минут)              │</t>
-        </is>
-      </c>
+          <t>БЛОК А. РЕКВИЗИТЫ АППАРАТА (для дальнейшего анализа)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Модель</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>└─────────────────────────────────────────────────────────────┘</t>
+          <t>Kyocera ECOSYS M3040dn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Серийный номер</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
+          <t>LS67Y43279</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Текст</t>
+          <t>Инвентарный номер</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>БЛОК А. РЕКВИЗИТЫ АППАРАТА (для дальнейшего анализа)</t>
+          <t>67+</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Локация (офис/кабинет)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
+          <t>Риелторы (Тюмень)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Kyocera ECOSYS M3040dn</t>
-        </is>
-      </c>
+          <t>Модель картриджа</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Серийный номер</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LS67Y43279</t>
-        </is>
-      </c>
+          <t>Текущий ресурс картриджа (%)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Инвентарный номер</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>67+</t>
-        </is>
-      </c>
+          <t>Дата последнего ТО</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Локация (офис/кабинет)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Риелторы (Тюмень)</t>
-        </is>
-      </c>
+          <t>Дата последней замены ЗИП</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Модель картриджа</t>
-        </is>
-      </c>
+          <t>Ответственный у Заказчика</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Текущий ресурс картриджа (%)</t>
-        </is>
-      </c>
+          <t>Контакт (тел/email)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Дата последнего ТО</t>
-        </is>
-      </c>
+          <t>БЛОК Б. ПРОВЕРКА ПО ШАГАМ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Дата последней замены ЗИП</t>
-        </is>
-      </c>
+          <t>ШАГ 1. ВНЕШНИЙ ОСМОТР (30 сек)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ответственный у Заказчика</t>
-        </is>
-      </c>
+          <t>Корпус, крышки, лотки — визуально целые</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Контакт (тел/email)</t>
-        </is>
-      </c>
+          <t>Кабели подключены надежно, без перегибов</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
-        </is>
-      </c>
+          <t>Вокруг аппарата чисто, нет мусора, скрепок, скоб</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>БЛОК Б. ПРОВЕРКА ПО ШАГАМ</t>
-        </is>
-      </c>
+          <t>ШАГ 2. СЧЕТЧИКИ (1 мин)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
-        </is>
-      </c>
+          <t>Открыть меню → Отчет → Страница состояния (Kyocera)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ШАГ 1. ВНЕШНИЙ ОСМОТР (30 сек)</t>
-        </is>
-      </c>
+          <t>или Меню → Reports → Usage Report (HP)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Корпус, крышки, лотки — визуально целые</t>
-        </is>
-      </c>
+          <t>Записать: Total / ЧБ / Цвет / Сканер</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Кабели подключены надежно, без перегибов</t>
-        </is>
-      </c>
+          <t>Сверить с данными в файле "Этажи покопийка AI.xlsx"</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Вокруг аппарата чисто, нет мусора, скрепок, скоб</t>
-        </is>
-      </c>
+          <t>(расхождение &gt; 5% — пометить в карточке)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ШАГ 2. СЧЕТЧИКИ (1 мин)</t>
-        </is>
-      </c>
+          <t>ШАГ 3. ТЕСТОВАЯ ПЕЧАТЬ (1 мин)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Открыть меню → Отчет → Страница состояния (Kyocera)</t>
-        </is>
-      </c>
+          <t>Распечатать тестовую страницу из встроенного меню</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>или Меню → Reports → Usage Report (HP)</t>
-        </is>
-      </c>
+          <t>Оценить: плотность, полосы, фон, регистрация</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Записать: Total / ЧБ / Цвет / Сканер</t>
-        </is>
-      </c>
+          <t>Проверить закрепление тонера (провести пальцем)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Сверить с данными в файле "Этажи покопийка AI.xlsx"</t>
-        </is>
-      </c>
+          <t>Для цветных — напечатать страницу качества цвета</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>(расхождение &gt; 5% — пометить в карточке)</t>
-        </is>
-      </c>
+          <t>ШАГ 4. ТЕСТ СКАНИРОВАНИЯ (1 мин)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ШАГ 3. ТЕСТОВАЯ ПЕЧАТЬ (1 мин)</t>
-        </is>
-      </c>
+          <t>Положить лист A4 на стекло / в ADF</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Распечатать тестовую страницу из встроенного меню</t>
-        </is>
-      </c>
+          <t>Отсканировать на email / в сетевую папку</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Оценить: плотность, полосы, фон, регистрация</t>
-        </is>
-      </c>
+          <t>Проверить: нет полос, захват ADF без перекоса</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Проверить закрепление тонера (провести пальцем)</t>
-        </is>
-      </c>
+          <t>ШАГ 5. ФИЗИКА (1-2 мин)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Для цветных — напечатать страницу качества цвета</t>
-        </is>
-      </c>
+          <t>Открыть переднюю крышку, заглянуть внутрь</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ШАГ 4. ТЕСТ СКАНИРОВАНИЯ (1 мин)</t>
-        </is>
-      </c>
+          <t>Осмотреть ролики захвата (лысые? грязные?)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Положить лист A4 на стекло / в ADF</t>
-        </is>
-      </c>
+          <t>Осмотреть термоузел (следы тонера, нагар?)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Отсканировать на email / в сетевую папку</t>
-        </is>
-      </c>
+          <t>Проверить дуплекс (нет ли замятой бумаги)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Проверить: нет полос, захват ADF без перекоса</t>
-        </is>
-      </c>
+          <t>Понюхать (запах гари = проблема с печкой)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ШАГ 5. ФИЗИКА (1-2 мин)</t>
-        </is>
-      </c>
+          <t>ШАГ 6. СУБЪЕКТИВНАЯ ОЦЕНКА (30 сек)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Открыть переднюю крышку, заглянуть внутрь</t>
-        </is>
-      </c>
+          <t>Оценить физическое состояние (1-5)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Осмотреть ролики захвата (лысые? грязные?)</t>
-        </is>
-      </c>
+          <t>Оценить качество печати (1-5)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Осмотреть термоузел (следы тонера, нагар?)</t>
-        </is>
-      </c>
+          <t>Оценить качество сканирования (1-5)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Проверить дуплекс (нет ли замятой бумаги)</t>
-        </is>
-      </c>
+          <t>Выставить общую оценку (1-5)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Понюхать (запах гари = проблема с печкой)</t>
-        </is>
-      </c>
+          <t>ШАГ 7. ФИКСАЦИЯ В КАРТОЧКЕ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ШАГ 6. СУБЪЕКТИВНАЯ ОЦЕНКА (30 сек)</t>
-        </is>
-      </c>
+          <t>Заполнить все поля карточки аппарата</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Оценить физическое состояние (1-5)</t>
-        </is>
-      </c>
+          <t>Отметить все применимые пункты "План действий"</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Оценить качество печати (1-5)</t>
-        </is>
-      </c>
+          <t>Указать приоритет и срок выполнения</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Оценить качество сканирования (1-5)</t>
-        </is>
-      </c>
+          <t>Сфотографировать дефекты (если есть)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Выставить общую оценку (1-5)</t>
-        </is>
-      </c>
+          <t>🚨 КРАСНЫЕ ФЛАГИ (немедленная эскалация Наталье, руководителю)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ШАГ 7. ФИКСАЦИЯ В КАРТОЧКЕ</t>
-        </is>
-      </c>
+          <t>• Аппарат не включается / нет реакции</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Заполнить все поля карточки аппарата</t>
-        </is>
-      </c>
+          <t>• Счетчик не изменился с прошлого месяца (0 отпечатков)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Отметить все применимые пункты "План действий"</t>
-        </is>
-      </c>
+          <t>• Сильный запах гари, дым</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Указать приоритет и срок выполнения</t>
-        </is>
-      </c>
+          <t>• Треск, скрежет, посторонние звуки</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Сфотографировать дефекты (если есть)</t>
-        </is>
-      </c>
+          <t>• Явное физическое повреждение корпуса/лотков</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
-        </is>
-      </c>
+          <t>• Оценка "1" по любому из параметров</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>🚨 КРАСНЫЕ ФЛАГИ (немедленная эскалация Наталье, руководителю)</t>
-        </is>
-      </c>
+          <t>• Аппарат отсутствует на месте (пропажа / перемещение без согласования)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>• Аппарат не включается / нет реакции</t>
-        </is>
-      </c>
+          <t>• Конфликт с Заказчиком / отказ в доступе</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>• Счетчик не изменился с прошлого месяца (0 отпечатков)</t>
-        </is>
-      </c>
+          <t>• Риск срыва SLA (критичный фронт-офис не работает)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Текст</t>
+          <t>Канал эскалации</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>• Сильный запах гари, дым</t>
+          <t>мессенджер MAX → чат "Этажи_Сервис"</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Текст</t>
+          <t>Время реакции Натальи</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>• Треск, скрежет, посторонние звуки</t>
+          <t>до 30 минут в рабочее время</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>• Явное физическое повреждение корпуса/лотков</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>• Оценка "1" по любому из параметров</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>• Аппарат отсутствует на месте (пропажа / перемещение без согласования)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>• Конфликт с Заказчиком / отказ в доступе</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>• Риск срыва SLA (критичный фронт-офис не работает)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Канал эскалации</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>мессенджер MAX → чат "Этажи_Сервис"</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Время реакции Натальи</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>до 30 минут в рабочее время</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
